--- a/template-non-multi.xlsx
+++ b/template-non-multi.xlsx
@@ -1,37 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SourceBuild\poi-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE872F47-8B2B-4E14-BA1A-50F232715081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5175" yWindow="1800" windowWidth="28035" windowHeight="17445" activeTab="2"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
     <sheet name="config" sheetId="2" r:id="rId2"/>
     <sheet name="data" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>AdonisGM</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -56,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B2" authorId="0" shapeId="0">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -81,7 +93,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B4" authorId="0" shapeId="0">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -105,7 +117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C4" authorId="0" shapeId="0">
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -129,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D4" authorId="0" shapeId="0">
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -381,8 +393,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -401,6 +413,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -426,6 +439,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -433,6 +447,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -440,6 +455,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -454,6 +470,7 @@
       <sz val="8"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -637,24 +654,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -667,6 +666,24 @@
     <xf numFmtId="49" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -687,10 +704,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1009,26 +1022,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.33203125" customWidth="1"/>
-    <col min="2" max="3" width="14.44140625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" width="27.375" customWidth="1"/>
+    <col min="2" max="3" width="14.5" style="8" customWidth="1"/>
+    <col min="4" max="4" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="9" t="s">
         <v>10</v>
@@ -1040,15 +1053,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="21"/>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="33"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>23</v>
       </c>
@@ -1059,7 +1072,7 @@
       <c r="C7" s="12"/>
       <c r="D7" s="13"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>22</v>
       </c>
@@ -1073,26 +1086,26 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="15"/>
       <c r="B9" s="16"/>
       <c r="C9" s="17"/>
       <c r="D9" s="18"/>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="22" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="24"/>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="36"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1108,23 +1121,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="11.44140625" style="2"/>
-    <col min="4" max="4" width="16.109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.44140625" style="2"/>
+    <col min="1" max="1" width="17.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.5" style="2"/>
+    <col min="4" max="4" width="16.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -1132,7 +1145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -1140,7 +1153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1154,7 +1167,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -1169,7 +1182,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
@@ -1191,491 +1204,490 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" style="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.21875" style="26" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="26"/>
+    <col min="1" max="1" width="6.875" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.75" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.875" style="20" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.25" style="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.875" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="25" customFormat="1" ht="18" customHeight="1">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:11" s="19" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="K1" s="21" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18" customHeight="1">
-      <c r="A2" s="28">
+    <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="22">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="34" t="s">
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="28" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="28">
+    <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="22">
         <v>1</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="34" t="s">
+      <c r="F3" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="34" t="s">
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="28" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="18" customHeight="1">
-      <c r="A4" s="28">
+    <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="22">
         <v>1</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="34" t="s">
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="28" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18" customHeight="1">
-      <c r="A5" s="28">
+    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="22">
         <v>1</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="35" t="s">
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="35" t="s">
+      <c r="K5" s="29" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18" customHeight="1">
-      <c r="A6" s="28">
+    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="22">
         <v>1</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="35" t="s">
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="35" t="s">
+      <c r="I6" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="35" t="s">
+      <c r="J6" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="35" t="s">
+      <c r="K6" s="29" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18" customHeight="1">
-      <c r="A7" s="31" t="s">
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="30" t="s">
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="24" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1">
-      <c r="A8" s="31" t="s">
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="30" t="s">
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="24" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18" customHeight="1">
-      <c r="A9" s="31" t="s">
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="31" t="s">
+      <c r="D9" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="30" t="s">
+      <c r="G9" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="30" t="s">
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="24" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18" customHeight="1">
-      <c r="A10" s="31" t="s">
+    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32" t="s">
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="32" t="s">
+      <c r="I10" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="J10" s="32" t="s">
+      <c r="J10" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="32" t="s">
+      <c r="K10" s="26" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18" customHeight="1">
-      <c r="A11" s="31" t="s">
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32" t="s">
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="32" t="s">
+      <c r="I11" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="32" t="s">
+      <c r="J11" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="K11" s="32" t="s">
+      <c r="K11" s="26" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18" customHeight="1">
-      <c r="A12" s="33" t="s">
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="29" t="s">
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1">
-      <c r="A13" s="33" t="s">
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="29" t="s">
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18" customHeight="1">
-      <c r="A14" s="33" t="s">
+    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="29" t="s">
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18" customHeight="1">
-      <c r="A15" s="33" t="s">
+    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="36" t="s">
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="I15" s="36" t="s">
+      <c r="I15" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="J15" s="36" t="s">
+      <c r="J15" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="K15" s="36" t="s">
+      <c r="K15" s="30" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18" customHeight="1">
-      <c r="A16" s="33" t="s">
+    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="36" t="s">
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="I16" s="36" t="s">
+      <c r="I16" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="J16" s="36" t="s">
+      <c r="J16" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="K16" s="36" t="s">
+      <c r="K16" s="30" t="s">
         <v>68</v>
       </c>
     </row>
